--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
         <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F9" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="G9" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>92.42</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="M9" t="n">
-        <v>36.58</v>
+        <v>36.65</v>
       </c>
       <c r="N9" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="O9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="P9" t="n">
-        <v>9.789999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.58</v>
+        <v>12.5</v>
       </c>
       <c r="R9" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="S9" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51.58</v>
+        <v>51.45</v>
       </c>
       <c r="Y9" t="n">
         <v>0.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.11</v>
+        <v>14.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.58</v>
+        <v>8.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.53</v>
+        <v>5.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.89</v>
+        <v>11.9</v>
       </c>
       <c r="AD9" t="n">
         <v>1.47</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
         <v>0.22</v>
@@ -4371,64 +4371,64 @@
         <v>1.78</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.65</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="BO9" t="n">
         <v>1.08</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.78</v>
+        <v>4.76</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.86</v>
+        <v>4.79</v>
       </c>
       <c r="BR9" t="n">
-        <v>97.3</v>
+        <v>97.37</v>
       </c>
       <c r="BS9" t="n">
-        <v>64.86</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>54.05</v>
+        <v>55.26</v>
       </c>
       <c r="BU9" t="n">
-        <v>27.03</v>
+        <v>28.95</v>
       </c>
       <c r="BV9" t="n">
-        <v>18.92</v>
+        <v>18.42</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.109999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="BX9" t="n">
-        <v>51.35</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="CA9" t="n">
         <v>3.71</v>
@@ -4446,22 +4446,22 @@
         <v>1.25</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CH9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CJ9" t="n">
         <v>1.52</v>
       </c>
-      <c r="CI9" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>1.53</v>
-      </c>
       <c r="CK9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL9" t="n">
         <v>1.88</v>
@@ -4476,28 +4476,28 @@
         <v>1.15</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CT9" t="n">
         <v>3.28</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CX9" t="n">
         <v>1.61</v>
@@ -4509,91 +4509,91 @@
         <v>2.27</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB9" t="n">
         <v>1.2</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="DE9" t="n">
         <v>0.16</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="DG9" t="n">
         <v>2.11</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.81</v>
+        <v>79.13</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DK9" t="n">
         <v>4.24</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="DM9" t="n">
-        <v>32.89</v>
+        <v>33.03</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.24</v>
+        <v>10.18</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.65</v>
+        <v>11.63</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.62</v>
+        <v>7.61</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.27</v>
+        <v>48.29</v>
       </c>
       <c r="DW9" t="n">
         <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.41</v>
+        <v>13.42</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.029999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.38</v>
+        <v>5.37</v>
       </c>
       <c r="EA9" t="n">
-        <v>11.94</v>
+        <v>11.95</v>
       </c>
       <c r="EB9" t="n">
         <v>1.39</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" t="n">
         <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
         <v>0.16</v>
@@ -5499,34 +5499,34 @@
         <v>2.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="AI12" t="n">
-        <v>83.11</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.72</v>
+        <v>4.58</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AN12" t="n">
-        <v>40.11</v>
+        <v>39.63</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="AP12" t="n">
         <v>1.89</v>
@@ -5535,16 +5535,16 @@
         <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.39</v>
+        <v>12.16</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.89</v>
+        <v>6.21</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AV12" t="n">
         <v>0.11</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>58.39</v>
+        <v>58</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.11</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.28</v>
+        <v>11.42</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.11</v>
+        <v>6.21</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.17</v>
+        <v>5.21</v>
       </c>
       <c r="BD12" t="n">
-        <v>10</v>
+        <v>10.16</v>
       </c>
       <c r="BE12" t="n">
         <v>1.37</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="BG12" t="n">
         <v>3.97</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.92</v>
+        <v>8.84</v>
       </c>
       <c r="BI12" t="n">
         <v>3.97</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.81</v>
+        <v>4.74</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.59</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>89.19</v>
+        <v>89.47</v>
       </c>
       <c r="BT12" t="n">
-        <v>81.08</v>
+        <v>81.58</v>
       </c>
       <c r="BU12" t="n">
-        <v>59.46</v>
+        <v>60.53</v>
       </c>
       <c r="BV12" t="n">
-        <v>40.54</v>
+        <v>39.47</v>
       </c>
       <c r="BW12" t="n">
-        <v>21.62</v>
+        <v>21.05</v>
       </c>
       <c r="BX12" t="n">
-        <v>72.97</v>
+        <v>71.05</v>
       </c>
       <c r="BY12" t="n">
         <v>1.65</v>
@@ -5640,19 +5640,19 @@
         <v>1.69</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="CC12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CD12" t="n">
         <v>2.51</v>
       </c>
-      <c r="CD12" t="n">
-        <v>2.53</v>
-      </c>
       <c r="CE12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CF12" t="n">
         <v>2.11</v>
@@ -5670,7 +5670,7 @@
         <v>1.46</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CL12" t="n">
         <v>1.98</v>
@@ -5688,7 +5688,7 @@
         <v>1.44</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CR12" t="n">
         <v>1.37</v>
@@ -5733,43 +5733,43 @@
         <v>0.16</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.75</v>
+        <v>85.52</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.78</v>
+        <v>4.71</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="DM12" t="n">
-        <v>36.76</v>
+        <v>36.6</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="DO12" t="n">
         <v>2.24</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.49</v>
+        <v>11.48</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.62</v>
+        <v>11.52</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.84</v>
+        <v>6</v>
       </c>
       <c r="DS12" t="n">
         <v>0.05</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>56.81</v>
+        <v>56.66</v>
       </c>
       <c r="DW12" t="n">
         <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.22</v>
+        <v>13.24</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.54</v>
+        <v>7.55</v>
       </c>
       <c r="DZ12" t="n">
         <v>5.68</v>
       </c>
       <c r="EA12" t="n">
-        <v>8.33</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="EB12" t="n">
         <v>1.5</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="13">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" t="n">
         <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
         <v>0.06</v>
@@ -6305,139 +6305,139 @@
         <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AI14" t="n">
-        <v>88.17</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.78</v>
+        <v>4.37</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="AN14" t="n">
-        <v>35.22</v>
+        <v>38.11</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.28</v>
+        <v>12.63</v>
       </c>
       <c r="AR14" t="n">
-        <v>11.89</v>
+        <v>12.21</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.72</v>
+        <v>6.74</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AU14" t="n">
         <v>2.11</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>48.83</v>
+        <v>49.21</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="BA14" t="n">
-        <v>12.83</v>
+        <v>13.47</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.33</v>
+        <v>7.84</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.5</v>
+        <v>5.63</v>
       </c>
       <c r="BD14" t="n">
-        <v>12</v>
+        <v>13.16</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.109999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.39</v>
+        <v>4.49</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>75</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>58.33</v>
+        <v>59.46</v>
       </c>
       <c r="BU14" t="n">
-        <v>44.44</v>
+        <v>45.95</v>
       </c>
       <c r="BV14" t="n">
-        <v>22.22</v>
+        <v>21.62</v>
       </c>
       <c r="BW14" t="n">
-        <v>11.11</v>
+        <v>10.81</v>
       </c>
       <c r="BX14" t="n">
-        <v>52.78</v>
+        <v>54.05</v>
       </c>
       <c r="BY14" t="n">
         <v>1.59</v>
@@ -6446,28 +6446,28 @@
         <v>1.59</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="CE14" t="n">
         <v>1.31</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI14" t="n">
         <v>2.18</v>
@@ -6512,7 +6512,7 @@
         <v>2.3</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX14" t="n">
         <v>1.52</v>
@@ -6536,46 +6536,46 @@
         <v>2.78</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="DH14" t="n">
-        <v>97.89</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.61</v>
+        <v>4.89</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.36</v>
+        <v>47.54</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.08</v>
+        <v>12.27</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.66</v>
+        <v>11.84</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.97</v>
+        <v>6</v>
       </c>
       <c r="DS14" t="n">
         <v>0.19</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.88</v>
+        <v>52</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX14" t="n">
-        <v>14.08</v>
+        <v>14.37</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.359999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.72</v>
+        <v>5.78</v>
       </c>
       <c r="EA14" t="n">
-        <v>13.75</v>
+        <v>14.3</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="15">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" t="n">
         <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
         <v>0.06</v>
@@ -8323,136 +8323,136 @@
         <v>0.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AI19" t="n">
-        <v>91.47</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="AJ19" t="n">
         <v>-0.05</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>37.79</v>
+        <v>37.3</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.32</v>
+        <v>11.3</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.42</v>
+        <v>10.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.53</v>
+        <v>7.8</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>53.74</v>
+        <v>53.55</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>11.11</v>
+        <v>10.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.89</v>
+        <v>6.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>12.16</v>
+        <v>12.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.54</v>
+        <v>10.55</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.43</v>
+        <v>5.39</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.05</v>
+        <v>5.11</v>
       </c>
       <c r="BR19" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS19" t="n">
-        <v>67.56999999999999</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>54.05</v>
+        <v>52.63</v>
       </c>
       <c r="BU19" t="n">
-        <v>32.43</v>
+        <v>31.58</v>
       </c>
       <c r="BV19" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="BW19" t="n">
-        <v>5.41</v>
+        <v>5.26</v>
       </c>
       <c r="BX19" t="n">
-        <v>48.65</v>
+        <v>47.37</v>
       </c>
       <c r="BY19" t="n">
         <v>1.96</v>
@@ -8467,28 +8467,28 @@
         <v>3.76</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.51</v>
+        <v>3.59</v>
       </c>
       <c r="CE19" t="n">
         <v>1.31</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CH19" t="n">
         <v>1.52</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CK19" t="n">
         <v>1.45</v>
@@ -8506,28 +8506,28 @@
         <v>1.21</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX19" t="n">
         <v>1.51</v>
@@ -8545,85 +8545,85 @@
         <v>1.22</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="DE19" t="n">
         <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="DH19" t="n">
-        <v>92.27</v>
+        <v>92.08</v>
       </c>
       <c r="DI19" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.4</v>
+        <v>41.05</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.84</v>
+        <v>11.82</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10.81</v>
+        <v>11</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.03</v>
+        <v>7.18</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.14</v>
+        <v>54.03</v>
       </c>
       <c r="DW19" t="n">
         <v>0.03</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.49</v>
+        <v>12.29</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.109999999999999</v>
+        <v>7.92</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
       <c r="EA19" t="n">
-        <v>13.35</v>
+        <v>13.63</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="20">
@@ -9439,61 +9439,61 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
         <v>18</v>
       </c>
       <c r="E22" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="F22" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="G22" t="n">
-        <v>3.83</v>
+        <v>3.95</v>
       </c>
       <c r="H22" t="n">
-        <v>90.78</v>
+        <v>92.58</v>
       </c>
       <c r="I22" t="n">
         <v>0.11</v>
       </c>
       <c r="J22" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="K22" t="n">
-        <v>7.06</v>
+        <v>7.11</v>
       </c>
       <c r="L22" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="M22" t="n">
-        <v>38.83</v>
+        <v>40.47</v>
       </c>
       <c r="N22" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="O22" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="P22" t="n">
-        <v>12.67</v>
+        <v>12.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>11.44</v>
+        <v>11.32</v>
       </c>
       <c r="R22" t="n">
-        <v>6.17</v>
+        <v>5.95</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="T22" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -9505,28 +9505,28 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>49.44</v>
+        <v>49.47</v>
       </c>
       <c r="Y22" t="n">
         <v>0.11</v>
       </c>
       <c r="Z22" t="n">
-        <v>17</v>
+        <v>17.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>10.83</v>
+        <v>10.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>6.17</v>
+        <v>6.11</v>
       </c>
       <c r="AC22" t="n">
-        <v>12.33</v>
+        <v>13.53</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="AF22" t="n">
         <v>0.17</v>
@@ -9610,70 +9610,70 @@
         <v>2.72</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="BH22" t="n">
-        <v>10.19</v>
+        <v>10.22</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="BN22" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="BO22" t="n">
         <v>1.19</v>
       </c>
       <c r="BP22" t="n">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="BQ22" t="n">
-        <v>5.61</v>
+        <v>5.65</v>
       </c>
       <c r="BR22" t="n">
-        <v>94.44</v>
+        <v>94.59</v>
       </c>
       <c r="BS22" t="n">
-        <v>66.67</v>
+        <v>64.86</v>
       </c>
       <c r="BT22" t="n">
-        <v>52.78</v>
+        <v>51.35</v>
       </c>
       <c r="BU22" t="n">
-        <v>30.56</v>
+        <v>29.73</v>
       </c>
       <c r="BV22" t="n">
-        <v>16.67</v>
+        <v>16.22</v>
       </c>
       <c r="BW22" t="n">
-        <v>11.11</v>
+        <v>10.81</v>
       </c>
       <c r="BX22" t="n">
-        <v>41.67</v>
+        <v>40.54</v>
       </c>
       <c r="BY22" t="n">
         <v>1.86</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CA22" t="n">
         <v>3.74</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CC22" t="n">
         <v>3.15</v>
@@ -9685,16 +9685,16 @@
         <v>1.29</v>
       </c>
       <c r="CF22" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CG22" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CH22" t="n">
         <v>1.54</v>
       </c>
       <c r="CI22" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CJ22" t="n">
         <v>1.58</v>
@@ -9709,34 +9709,34 @@
         <v>2.52</v>
       </c>
       <c r="CN22" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO22" t="n">
         <v>1.18</v>
       </c>
       <c r="CP22" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ22" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CR22" t="n">
         <v>1.36</v>
       </c>
       <c r="CS22" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CT22" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CU22" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV22" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW22" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX22" t="n">
         <v>1.52</v>
@@ -9751,88 +9751,88 @@
         <v>2.01</v>
       </c>
       <c r="DB22" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC22" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DD22" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF22" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DG22" t="n">
-        <v>3.33</v>
+        <v>3.41</v>
       </c>
       <c r="DH22" t="n">
-        <v>90.42</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="DI22" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DJ22" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="DK22" t="n">
-        <v>6.11</v>
+        <v>6.17</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DM22" t="n">
-        <v>38.58</v>
+        <v>39.43</v>
       </c>
       <c r="DN22" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO22" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="DP22" t="n">
         <v>14.22</v>
       </c>
       <c r="DQ22" t="n">
-        <v>12.56</v>
+        <v>12.46</v>
       </c>
       <c r="DR22" t="n">
-        <v>6.7</v>
+        <v>6.57</v>
       </c>
       <c r="DS22" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT22" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU22" t="n">
         <v>0</v>
       </c>
       <c r="DV22" t="n">
-        <v>48.08</v>
+        <v>48.13</v>
       </c>
       <c r="DW22" t="n">
         <v>0.11</v>
       </c>
       <c r="DX22" t="n">
-        <v>15.36</v>
+        <v>15.43</v>
       </c>
       <c r="DY22" t="n">
-        <v>10.42</v>
+        <v>10.49</v>
       </c>
       <c r="DZ22" t="n">
-        <v>4.94</v>
+        <v>4.95</v>
       </c>
       <c r="EA22" t="n">
-        <v>12.92</v>
+        <v>13.52</v>
       </c>
       <c r="EB22" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="EC22" t="n">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="23">
@@ -13066,10 +13066,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D31" t="n">
         <v>18</v>
@@ -13078,82 +13078,82 @@
         <v>0.11</v>
       </c>
       <c r="F31" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="G31" t="n">
-        <v>3.83</v>
+        <v>3.68</v>
       </c>
       <c r="H31" t="n">
-        <v>100.33</v>
+        <v>100.79</v>
       </c>
       <c r="I31" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="J31" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="K31" t="n">
-        <v>6.83</v>
+        <v>6.74</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="M31" t="n">
-        <v>57.17</v>
+        <v>56.74</v>
       </c>
       <c r="N31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P31" t="n">
-        <v>12.83</v>
+        <v>13.11</v>
       </c>
       <c r="Q31" t="n">
-        <v>12.17</v>
+        <v>12.42</v>
       </c>
       <c r="R31" t="n">
-        <v>5.83</v>
+        <v>6.32</v>
       </c>
       <c r="S31" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U31" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="V31" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>55.94</v>
+        <v>55.32</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="Z31" t="n">
-        <v>17.61</v>
+        <v>17.16</v>
       </c>
       <c r="AA31" t="n">
-        <v>11.44</v>
+        <v>11</v>
       </c>
       <c r="AB31" t="n">
-        <v>6.17</v>
+        <v>6.16</v>
       </c>
       <c r="AC31" t="n">
-        <v>14</v>
+        <v>14.11</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="AF31" t="n">
         <v>0.17</v>
@@ -13237,67 +13237,67 @@
         <v>2.22</v>
       </c>
       <c r="BG31" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="BH31" t="n">
-        <v>10.81</v>
+        <v>11.05</v>
       </c>
       <c r="BI31" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="BK31" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="BL31" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BM31" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BN31" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BP31" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
       <c r="BQ31" t="n">
-        <v>5.64</v>
+        <v>5.7</v>
       </c>
       <c r="BR31" t="n">
-        <v>88.89</v>
+        <v>89.19</v>
       </c>
       <c r="BS31" t="n">
-        <v>83.33</v>
+        <v>83.78</v>
       </c>
       <c r="BT31" t="n">
-        <v>63.89</v>
+        <v>64.86</v>
       </c>
       <c r="BU31" t="n">
-        <v>30.56</v>
+        <v>32.43</v>
       </c>
       <c r="BV31" t="n">
-        <v>19.44</v>
+        <v>18.92</v>
       </c>
       <c r="BW31" t="n">
-        <v>8.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BX31" t="n">
-        <v>55.56</v>
+        <v>56.76</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BZ31" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CA31" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CB31" t="n">
         <v>4.06</v>
@@ -13312,7 +13312,7 @@
         <v>1.29</v>
       </c>
       <c r="CF31" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CG31" t="n">
         <v>3.38</v>
@@ -13333,13 +13333,13 @@
         <v>1.77</v>
       </c>
       <c r="CM31" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CN31" t="n">
         <v>2.01</v>
       </c>
       <c r="CO31" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP31" t="n">
         <v>1.65</v>
@@ -13369,10 +13369,10 @@
         <v>1.51</v>
       </c>
       <c r="CY31" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CZ31" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DA31" t="n">
         <v>2.06</v>
@@ -13390,76 +13390,76 @@
         <v>0.14</v>
       </c>
       <c r="DF31" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="DG31" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="DH31" t="n">
-        <v>86.66</v>
+        <v>87.27</v>
       </c>
       <c r="DI31" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ31" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="DK31" t="n">
-        <v>6.11</v>
+        <v>6.08</v>
       </c>
       <c r="DL31" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="DM31" t="n">
-        <v>45.92</v>
+        <v>46</v>
       </c>
       <c r="DN31" t="n">
         <v>0.7</v>
       </c>
       <c r="DO31" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="DP31" t="n">
-        <v>13.38</v>
+        <v>13.51</v>
       </c>
       <c r="DQ31" t="n">
-        <v>11.67</v>
+        <v>11.81</v>
       </c>
       <c r="DR31" t="n">
-        <v>6.28</v>
+        <v>6.51</v>
       </c>
       <c r="DS31" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT31" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU31" t="n">
         <v>0</v>
       </c>
       <c r="DV31" t="n">
-        <v>54.08</v>
+        <v>53.81</v>
       </c>
       <c r="DW31" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="DX31" t="n">
-        <v>14.64</v>
+        <v>14.49</v>
       </c>
       <c r="DY31" t="n">
-        <v>9.44</v>
+        <v>9.27</v>
       </c>
       <c r="DZ31" t="n">
-        <v>5.19</v>
+        <v>5.22</v>
       </c>
       <c r="EA31" t="n">
-        <v>15</v>
+        <v>15.03</v>
       </c>
       <c r="EB31" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="EC31" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
@@ -5102,7 +5102,7 @@
         <v>1.65</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
         <v>69.06</v>
@@ -5117,7 +5117,7 @@
         <v>4.18</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="AN11" t="n">
         <v>36.82</v>
@@ -5126,7 +5126,7 @@
         <v>1.06</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AQ11" t="n">
         <v>14.41</v>
@@ -5204,10 +5204,10 @@
         <v>1.21</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="BR11" t="n">
         <v>91.18000000000001</v>
@@ -5333,7 +5333,7 @@
         <v>1.59</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DH11" t="n">
         <v>78.23999999999999</v>
@@ -5348,7 +5348,7 @@
         <v>5.03</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="DM11" t="n">
         <v>42.27</v>
@@ -5357,7 +5357,7 @@
         <v>1.09</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="DP11" t="n">
         <v>14.68</v>
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
         <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
         <v>0.11</v>
@@ -6711,136 +6711,136 @@
         <v>0.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AI15" t="n">
-        <v>67.67</v>
+        <v>67.11</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.94</v>
+        <v>3.79</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AN15" t="n">
-        <v>37.39</v>
+        <v>37.32</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.94</v>
+        <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>10.61</v>
+        <v>10.79</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.720000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>37.22</v>
+        <v>36.74</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.78</v>
+        <v>10.79</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.72</v>
+        <v>6.74</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="BD15" t="n">
-        <v>13.78</v>
+        <v>14.05</v>
       </c>
       <c r="BE15" t="n">
         <v>1.23</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.970000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="BL15" t="n">
         <v>0.89</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.97</v>
+        <v>4.87</v>
       </c>
       <c r="BR15" t="n">
-        <v>89.19</v>
+        <v>89.47</v>
       </c>
       <c r="BS15" t="n">
-        <v>75.68000000000001</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>59.46</v>
+        <v>57.89</v>
       </c>
       <c r="BU15" t="n">
-        <v>35.14</v>
+        <v>34.21</v>
       </c>
       <c r="BV15" t="n">
-        <v>18.92</v>
+        <v>18.42</v>
       </c>
       <c r="BW15" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="BX15" t="n">
-        <v>59.46</v>
+        <v>57.89</v>
       </c>
       <c r="BY15" t="n">
         <v>1.84</v>
@@ -6849,16 +6849,16 @@
         <v>2.04</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="CE15" t="n">
         <v>1.28</v>
@@ -6867,10 +6867,10 @@
         <v>2.41</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI15" t="n">
         <v>2.14</v>
@@ -6882,19 +6882,19 @@
         <v>1.39</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO15" t="n">
         <v>1.18</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CQ15" t="n">
         <v>2.69</v>
@@ -6918,67 +6918,67 @@
         <v>1.67</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB15" t="n">
         <v>1.23</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="DE15" t="n">
         <v>0.11</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DH15" t="n">
-        <v>74.27</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.54</v>
+        <v>4.45</v>
       </c>
       <c r="DL15" t="n">
         <v>0.14</v>
       </c>
       <c r="DM15" t="n">
-        <v>40.97</v>
+        <v>40.85</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.03</v>
+        <v>13.06</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.73</v>
+        <v>10.82</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.32</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DS15" t="n">
         <v>0.11</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>39.1</v>
+        <v>38.82</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.84</v>
+        <v>11.82</v>
       </c>
       <c r="DY15" t="n">
         <v>7.16</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.46</v>
+        <v>15.55</v>
       </c>
       <c r="EB15" t="n">
         <v>1.37</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="16">
@@ -7842,7 +7842,7 @@
         <v>1.47</v>
       </c>
       <c r="G18" t="n">
-        <v>2.41</v>
+        <v>2.18</v>
       </c>
       <c r="H18" t="n">
         <v>75.94</v>
@@ -7857,7 +7857,7 @@
         <v>5.29</v>
       </c>
       <c r="L18" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="M18" t="n">
         <v>35.88</v>
@@ -7866,7 +7866,7 @@
         <v>0.65</v>
       </c>
       <c r="O18" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
         <v>12.71</v>
@@ -8025,10 +8025,10 @@
         <v>1.15</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.32</v>
+        <v>4.21</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.26</v>
+        <v>4.09</v>
       </c>
       <c r="BR18" t="n">
         <v>91.18000000000001</v>
@@ -8154,7 +8154,7 @@
         <v>1.38</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="DH18" t="n">
         <v>76.53</v>
@@ -8169,7 +8169,7 @@
         <v>5.03</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM18" t="n">
         <v>33.91</v>
@@ -8178,7 +8178,7 @@
         <v>0.65</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="DP18" t="n">
         <v>12.03</v>
@@ -9535,7 +9535,7 @@
         <v>1.89</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.83</v>
+        <v>2.67</v>
       </c>
       <c r="AI22" t="n">
         <v>90.06</v>
@@ -9550,7 +9550,7 @@
         <v>5.17</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="AN22" t="n">
         <v>38.33</v>
@@ -9559,7 +9559,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="AQ22" t="n">
         <v>15.78</v>
@@ -9637,10 +9637,10 @@
         <v>1.19</v>
       </c>
       <c r="BP22" t="n">
-        <v>4.49</v>
+        <v>4.38</v>
       </c>
       <c r="BQ22" t="n">
-        <v>5.65</v>
+        <v>5.49</v>
       </c>
       <c r="BR22" t="n">
         <v>94.59</v>
@@ -9766,7 +9766,7 @@
         <v>1.71</v>
       </c>
       <c r="DG22" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="DH22" t="n">
         <v>91.34999999999999</v>
@@ -9781,7 +9781,7 @@
         <v>6.17</v>
       </c>
       <c r="DL22" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM22" t="n">
         <v>39.43</v>
@@ -9790,7 +9790,7 @@
         <v>0.89</v>
       </c>
       <c r="DO22" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="DP22" t="n">
         <v>14.22</v>
@@ -11051,94 +11051,94 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D26" t="n">
         <v>18</v>
       </c>
       <c r="E26" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F26" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="G26" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="H26" t="n">
-        <v>95.31999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I26" t="n">
         <v>0.05</v>
       </c>
       <c r="J26" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="K26" t="n">
-        <v>6.53</v>
+        <v>6.45</v>
       </c>
       <c r="L26" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="M26" t="n">
-        <v>52.95</v>
+        <v>54.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="O26" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="P26" t="n">
-        <v>12.63</v>
+        <v>12.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>13.68</v>
+        <v>13.7</v>
       </c>
       <c r="R26" t="n">
-        <v>4.63</v>
+        <v>4.75</v>
       </c>
       <c r="S26" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="T26" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U26" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V26" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>62.42</v>
+        <v>62.9</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>14.95</v>
+        <v>14.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>9.529999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AB26" t="n">
-        <v>5.42</v>
+        <v>5.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>16.26</v>
+        <v>16.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AF26" t="n">
         <v>0.06</v>
@@ -11222,70 +11222,70 @@
         <v>1.67</v>
       </c>
       <c r="BG26" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="BH26" t="n">
-        <v>8.73</v>
+        <v>8.66</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="BL26" t="n">
         <v>0.76</v>
       </c>
       <c r="BM26" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BN26" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="BP26" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="BQ26" t="n">
-        <v>4.76</v>
+        <v>4.66</v>
       </c>
       <c r="BR26" t="n">
-        <v>91.89</v>
+        <v>92.11</v>
       </c>
       <c r="BS26" t="n">
-        <v>81.08</v>
+        <v>78.95</v>
       </c>
       <c r="BT26" t="n">
-        <v>62.16</v>
+        <v>60.53</v>
       </c>
       <c r="BU26" t="n">
-        <v>37.84</v>
+        <v>36.84</v>
       </c>
       <c r="BV26" t="n">
-        <v>21.62</v>
+        <v>21.05</v>
       </c>
       <c r="BW26" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="BX26" t="n">
-        <v>56.76</v>
+        <v>55.26</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CA26" t="n">
         <v>3.74</v>
       </c>
       <c r="CB26" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="CC26" t="n">
         <v>2.73</v>
@@ -11297,13 +11297,13 @@
         <v>1.22</v>
       </c>
       <c r="CF26" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CG26" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CH26" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CI26" t="n">
         <v>2.22</v>
@@ -11315,7 +11315,7 @@
         <v>1.45</v>
       </c>
       <c r="CL26" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM26" t="n">
         <v>2.25</v>
@@ -11327,7 +11327,7 @@
         <v>1.12</v>
       </c>
       <c r="CP26" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CQ26" t="n">
         <v>2.39</v>
@@ -11345,7 +11345,7 @@
         <v>1.59</v>
       </c>
       <c r="CV26" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CW26" t="n">
         <v>1.6</v>
@@ -11357,7 +11357,7 @@
         <v>1.94</v>
       </c>
       <c r="CZ26" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DA26" t="n">
         <v>1.87</v>
@@ -11372,79 +11372,79 @@
         <v>2.6</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF26" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="DG26" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="DH26" t="n">
-        <v>92.98</v>
+        <v>94.39</v>
       </c>
       <c r="DI26" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ26" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="DK26" t="n">
-        <v>5.38</v>
+        <v>5.37</v>
       </c>
       <c r="DL26" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="DM26" t="n">
-        <v>48.44</v>
+        <v>49.58</v>
       </c>
       <c r="DN26" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="DO26" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="DP26" t="n">
-        <v>12.43</v>
+        <v>12.39</v>
       </c>
       <c r="DQ26" t="n">
-        <v>13.46</v>
+        <v>13.47</v>
       </c>
       <c r="DR26" t="n">
-        <v>5.92</v>
+        <v>5.95</v>
       </c>
       <c r="DS26" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT26" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU26" t="n">
         <v>0</v>
       </c>
       <c r="DV26" t="n">
-        <v>61.46</v>
+        <v>61.73</v>
       </c>
       <c r="DW26" t="n">
         <v>0.03</v>
       </c>
       <c r="DX26" t="n">
-        <v>13.14</v>
+        <v>13.03</v>
       </c>
       <c r="DY26" t="n">
         <v>7.97</v>
       </c>
       <c r="DZ26" t="n">
-        <v>5.16</v>
+        <v>5.05</v>
       </c>
       <c r="EA26" t="n">
-        <v>15.62</v>
+        <v>15.55</v>
       </c>
       <c r="EB26" t="n">
         <v>1.54</v>
       </c>
       <c r="EC26" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="27">
@@ -11469,7 +11469,7 @@
         <v>1.11</v>
       </c>
       <c r="G27" t="n">
-        <v>2.89</v>
+        <v>2.61</v>
       </c>
       <c r="H27" t="n">
         <v>93.5</v>
@@ -11484,7 +11484,7 @@
         <v>4.89</v>
       </c>
       <c r="L27" t="n">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
       <c r="M27" t="n">
         <v>46</v>
@@ -11493,7 +11493,7 @@
         <v>0.61</v>
       </c>
       <c r="O27" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="P27" t="n">
         <v>11</v>
@@ -11652,10 +11652,10 @@
         <v>1.49</v>
       </c>
       <c r="BP27" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="BQ27" t="n">
-        <v>5.03</v>
+        <v>4.89</v>
       </c>
       <c r="BR27" t="n">
         <v>94.59</v>
@@ -11781,7 +11781,7 @@
         <v>1.08</v>
       </c>
       <c r="DG27" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="DH27" t="n">
         <v>96.05</v>
@@ -11796,7 +11796,7 @@
         <v>5.27</v>
       </c>
       <c r="DL27" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM27" t="n">
         <v>48.92</v>
@@ -11805,7 +11805,7 @@
         <v>0.68</v>
       </c>
       <c r="DO27" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DP27" t="n">
         <v>10.94</v>

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
@@ -5409,61 +5409,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="F12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
-        <v>88.26000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>-0.05</v>
       </c>
       <c r="J12" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="L12" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="M12" t="n">
-        <v>33.58</v>
+        <v>34.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="O12" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="P12" t="n">
-        <v>11.95</v>
+        <v>12.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.89</v>
+        <v>11.3</v>
       </c>
       <c r="R12" t="n">
-        <v>5.79</v>
+        <v>5.7</v>
       </c>
       <c r="S12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>55.32</v>
+        <v>55</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.05</v>
+        <v>14.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.890000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.16</v>
+        <v>6.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.74</v>
+        <v>6.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="AF12" t="n">
         <v>0.16</v>
@@ -5580,70 +5580,70 @@
         <v>2.05</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.84</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="BQ12" t="n">
         <v>4.74</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.73999999999999</v>
+        <v>94.87</v>
       </c>
       <c r="BS12" t="n">
-        <v>89.47</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>81.58</v>
+        <v>82.05</v>
       </c>
       <c r="BU12" t="n">
-        <v>60.53</v>
+        <v>61.54</v>
       </c>
       <c r="BV12" t="n">
-        <v>39.47</v>
+        <v>41.03</v>
       </c>
       <c r="BW12" t="n">
-        <v>21.05</v>
+        <v>23.08</v>
       </c>
       <c r="BX12" t="n">
-        <v>71.05</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.09</v>
+        <v>4.11</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="CC12" t="n">
         <v>2.48</v>
@@ -5658,7 +5658,7 @@
         <v>2.11</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="CH12" t="n">
         <v>1.7</v>
@@ -5673,7 +5673,7 @@
         <v>1.55</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM12" t="n">
         <v>2.31</v>
@@ -5694,7 +5694,7 @@
         <v>1.37</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CT12" t="n">
         <v>3.18</v>
@@ -5730,46 +5730,46 @@
         <v>2.18</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.52</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM12" t="n">
-        <v>36.6</v>
+        <v>37.15</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.48</v>
+        <v>11.72</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.52</v>
+        <v>11.72</v>
       </c>
       <c r="DR12" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="DS12" t="n">
         <v>0.05</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>56.66</v>
+        <v>56.46</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.24</v>
+        <v>13.2</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.55</v>
+        <v>7.51</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.68</v>
+        <v>5.69</v>
       </c>
       <c r="EA12" t="n">
-        <v>8.449999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="EB12" t="n">
         <v>1.5</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="13">
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" t="n">
         <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
         <v>0.06</v>
@@ -8323,49 +8323,49 @@
         <v>0.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
         <v>2.05</v>
       </c>
       <c r="AI19" t="n">
-        <v>91.15000000000001</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="AJ19" t="n">
         <v>-0.05</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.85</v>
+        <v>3.76</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="AN19" t="n">
-        <v>37.3</v>
+        <v>37.67</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.3</v>
+        <v>11.67</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.8</v>
+        <v>11.29</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.8</v>
+        <v>7.57</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AV19" t="n">
         <v>0.1</v>
@@ -8377,82 +8377,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>53.55</v>
+        <v>53.43</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.8</v>
+        <v>10.52</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.6</v>
+        <v>6.33</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="BD19" t="n">
-        <v>12.75</v>
+        <v>13.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.55</v>
+        <v>10.46</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.39</v>
+        <v>5.31</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="BR19" t="n">
-        <v>92.11</v>
+        <v>92.31</v>
       </c>
       <c r="BS19" t="n">
-        <v>65.79000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT19" t="n">
-        <v>52.63</v>
+        <v>53.85</v>
       </c>
       <c r="BU19" t="n">
-        <v>31.58</v>
+        <v>33.33</v>
       </c>
       <c r="BV19" t="n">
-        <v>10.53</v>
+        <v>12.82</v>
       </c>
       <c r="BW19" t="n">
-        <v>5.26</v>
+        <v>7.69</v>
       </c>
       <c r="BX19" t="n">
-        <v>47.37</v>
+        <v>48.72</v>
       </c>
       <c r="BY19" t="n">
         <v>1.96</v>
@@ -8461,43 +8461,43 @@
         <v>2.01</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.39</v>
+        <v>3.49</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.59</v>
+        <v>3.7</v>
       </c>
       <c r="CE19" t="n">
         <v>1.31</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="CH19" t="n">
         <v>1.52</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CK19" t="n">
         <v>1.45</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CN19" t="n">
         <v>1.95</v>
@@ -8506,22 +8506,22 @@
         <v>1.21</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CT19" t="n">
         <v>3.21</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV19" t="n">
         <v>2.39</v>
@@ -8530,16 +8530,16 @@
         <v>1.63</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DB19" t="n">
         <v>1.22</v>
@@ -8548,49 +8548,49 @@
         <v>1.73</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="DE19" t="n">
         <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="DH19" t="n">
-        <v>92.08</v>
+        <v>92.28</v>
       </c>
       <c r="DI19" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="DK19" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.05</v>
+        <v>41.15</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.82</v>
+        <v>12</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11</v>
+        <v>11.26</v>
       </c>
       <c r="DR19" t="n">
-        <v>7.18</v>
+        <v>7.08</v>
       </c>
       <c r="DS19" t="n">
         <v>0.13</v>
@@ -8602,28 +8602,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>54.03</v>
+        <v>53.95</v>
       </c>
       <c r="DW19" t="n">
         <v>0.03</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.29</v>
+        <v>12.1</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.92</v>
+        <v>7.74</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.37</v>
+        <v>4.36</v>
       </c>
       <c r="EA19" t="n">
-        <v>13.63</v>
+        <v>13.8</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -11051,10 +11051,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D26" t="n">
         <v>18</v>
@@ -11063,49 +11063,49 @@
         <v>0.1</v>
       </c>
       <c r="F26" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="G26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H26" t="n">
-        <v>97.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I26" t="n">
         <v>0.05</v>
       </c>
       <c r="J26" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="K26" t="n">
-        <v>6.45</v>
+        <v>6.38</v>
       </c>
       <c r="L26" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="M26" t="n">
-        <v>54.9</v>
+        <v>53.62</v>
       </c>
       <c r="N26" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="O26" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="P26" t="n">
-        <v>12.55</v>
+        <v>12.76</v>
       </c>
       <c r="Q26" t="n">
-        <v>13.7</v>
+        <v>14.1</v>
       </c>
       <c r="R26" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="S26" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="U26" t="n">
         <v>0.1</v>
@@ -11117,28 +11117,28 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>62.9</v>
+        <v>62.48</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="Z26" t="n">
-        <v>14.65</v>
+        <v>14.48</v>
       </c>
       <c r="AA26" t="n">
-        <v>9.449999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="AB26" t="n">
-        <v>5.2</v>
+        <v>5.14</v>
       </c>
       <c r="AC26" t="n">
-        <v>16.1</v>
+        <v>16.24</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AF26" t="n">
         <v>0.06</v>
@@ -11222,70 +11222,70 @@
         <v>1.67</v>
       </c>
       <c r="BG26" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="BH26" t="n">
-        <v>8.66</v>
+        <v>8.59</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="BL26" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM26" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="BN26" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BP26" t="n">
         <v>4</v>
       </c>
       <c r="BQ26" t="n">
-        <v>4.66</v>
+        <v>4.59</v>
       </c>
       <c r="BR26" t="n">
-        <v>92.11</v>
+        <v>92.31</v>
       </c>
       <c r="BS26" t="n">
-        <v>78.95</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="BT26" t="n">
-        <v>60.53</v>
+        <v>61.54</v>
       </c>
       <c r="BU26" t="n">
-        <v>36.84</v>
+        <v>38.46</v>
       </c>
       <c r="BV26" t="n">
-        <v>21.05</v>
+        <v>20.51</v>
       </c>
       <c r="BW26" t="n">
-        <v>10.53</v>
+        <v>10.26</v>
       </c>
       <c r="BX26" t="n">
-        <v>55.26</v>
+        <v>56.41</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="CA26" t="n">
         <v>3.74</v>
       </c>
       <c r="CB26" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="CC26" t="n">
         <v>2.73</v>
@@ -11300,13 +11300,13 @@
         <v>2.24</v>
       </c>
       <c r="CG26" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CH26" t="n">
         <v>1.49</v>
       </c>
       <c r="CI26" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CJ26" t="n">
         <v>1.49</v>
@@ -11357,7 +11357,7 @@
         <v>1.94</v>
       </c>
       <c r="CZ26" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DA26" t="n">
         <v>1.87</v>
@@ -11375,43 +11375,43 @@
         <v>0.08</v>
       </c>
       <c r="DF26" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="DG26" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="DH26" t="n">
-        <v>94.39</v>
+        <v>93.41</v>
       </c>
       <c r="DI26" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ26" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="DK26" t="n">
-        <v>5.37</v>
+        <v>5.36</v>
       </c>
       <c r="DL26" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DM26" t="n">
-        <v>49.58</v>
+        <v>49.03</v>
       </c>
       <c r="DN26" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO26" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="DP26" t="n">
-        <v>12.39</v>
+        <v>12.51</v>
       </c>
       <c r="DQ26" t="n">
-        <v>13.47</v>
+        <v>13.69</v>
       </c>
       <c r="DR26" t="n">
-        <v>5.95</v>
+        <v>5.92</v>
       </c>
       <c r="DS26" t="n">
         <v>0.13</v>
@@ -11423,28 +11423,28 @@
         <v>0</v>
       </c>
       <c r="DV26" t="n">
-        <v>61.73</v>
+        <v>61.54</v>
       </c>
       <c r="DW26" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="DX26" t="n">
-        <v>13.03</v>
+        <v>12.98</v>
       </c>
       <c r="DY26" t="n">
-        <v>7.97</v>
+        <v>7.95</v>
       </c>
       <c r="DZ26" t="n">
-        <v>5.05</v>
+        <v>5.02</v>
       </c>
       <c r="EA26" t="n">
-        <v>15.55</v>
+        <v>15.64</v>
       </c>
       <c r="EB26" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="EC26" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="27">
@@ -13066,13 +13066,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C31" t="n">
         <v>19</v>
       </c>
       <c r="D31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
         <v>0.11</v>
@@ -13156,139 +13156,139 @@
         <v>1.79</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AI31" t="n">
-        <v>73</v>
+        <v>71.89</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AL31" t="n">
-        <v>5.39</v>
+        <v>5.16</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="AN31" t="n">
-        <v>34.67</v>
+        <v>34.05</v>
       </c>
       <c r="AO31" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="AQ31" t="n">
-        <v>13.94</v>
+        <v>14.32</v>
       </c>
       <c r="AR31" t="n">
-        <v>11.17</v>
+        <v>11.47</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.72</v>
+        <v>6.63</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AX31" t="n">
         <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>52.22</v>
+        <v>51.89</v>
       </c>
       <c r="AZ31" t="n">
         <v>0.11</v>
       </c>
       <c r="BA31" t="n">
-        <v>11.67</v>
+        <v>11.63</v>
       </c>
       <c r="BB31" t="n">
-        <v>7.44</v>
+        <v>7.21</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.22</v>
+        <v>4.42</v>
       </c>
       <c r="BD31" t="n">
-        <v>16</v>
+        <v>15.53</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BF31" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="BG31" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="BH31" t="n">
-        <v>11.05</v>
+        <v>10.92</v>
       </c>
       <c r="BI31" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="BK31" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="BL31" t="n">
         <v>0.89</v>
       </c>
       <c r="BM31" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BN31" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BP31" t="n">
-        <v>5.16</v>
+        <v>5.13</v>
       </c>
       <c r="BQ31" t="n">
-        <v>5.7</v>
+        <v>5.61</v>
       </c>
       <c r="BR31" t="n">
-        <v>89.19</v>
+        <v>89.47</v>
       </c>
       <c r="BS31" t="n">
-        <v>83.78</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT31" t="n">
-        <v>64.86</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="BU31" t="n">
-        <v>32.43</v>
+        <v>34.21</v>
       </c>
       <c r="BV31" t="n">
-        <v>18.92</v>
+        <v>18.42</v>
       </c>
       <c r="BW31" t="n">
-        <v>8.109999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="BX31" t="n">
-        <v>56.76</v>
+        <v>57.89</v>
       </c>
       <c r="BY31" t="n">
         <v>1.81</v>
@@ -13297,16 +13297,16 @@
         <v>1.83</v>
       </c>
       <c r="CA31" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CB31" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="CC31" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CD31" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CE31" t="n">
         <v>1.29</v>
@@ -13315,19 +13315,19 @@
         <v>2.4</v>
       </c>
       <c r="CG31" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="CH31" t="n">
         <v>1.54</v>
       </c>
       <c r="CI31" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CJ31" t="n">
         <v>1.59</v>
       </c>
       <c r="CK31" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL31" t="n">
         <v>1.77</v>
@@ -13336,10 +13336,10 @@
         <v>2.64</v>
       </c>
       <c r="CN31" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CO31" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP31" t="n">
         <v>1.65</v>
@@ -13372,10 +13372,10 @@
         <v>1.76</v>
       </c>
       <c r="CZ31" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DA31" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DB31" t="n">
         <v>1.21</v>
@@ -13387,46 +13387,46 @@
         <v>2.67</v>
       </c>
       <c r="DE31" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="DF31" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DG31" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="DH31" t="n">
-        <v>87.27</v>
+        <v>86.34</v>
       </c>
       <c r="DI31" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="DJ31" t="n">
         <v>2.13</v>
       </c>
       <c r="DK31" t="n">
-        <v>6.08</v>
+        <v>5.95</v>
       </c>
       <c r="DL31" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="DM31" t="n">
-        <v>46</v>
+        <v>45.4</v>
       </c>
       <c r="DN31" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="DO31" t="n">
-        <v>2.97</v>
+        <v>2.89</v>
       </c>
       <c r="DP31" t="n">
-        <v>13.51</v>
+        <v>13.71</v>
       </c>
       <c r="DQ31" t="n">
-        <v>11.81</v>
+        <v>11.94</v>
       </c>
       <c r="DR31" t="n">
-        <v>6.51</v>
+        <v>6.48</v>
       </c>
       <c r="DS31" t="n">
         <v>0.24</v>
@@ -13438,22 +13438,22 @@
         <v>0</v>
       </c>
       <c r="DV31" t="n">
-        <v>53.81</v>
+        <v>53.6</v>
       </c>
       <c r="DW31" t="n">
         <v>0.11</v>
       </c>
       <c r="DX31" t="n">
-        <v>14.49</v>
+        <v>14.4</v>
       </c>
       <c r="DY31" t="n">
-        <v>9.27</v>
+        <v>9.1</v>
       </c>
       <c r="DZ31" t="n">
-        <v>5.22</v>
+        <v>5.29</v>
       </c>
       <c r="EA31" t="n">
-        <v>15.03</v>
+        <v>14.82</v>
       </c>
       <c r="EB31" t="n">
         <v>1.58</v>

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
@@ -13192,10 +13192,10 @@
         <v>14.32</v>
       </c>
       <c r="AR31" t="n">
-        <v>11.47</v>
+        <v>11.42</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.63</v>
+        <v>6.68</v>
       </c>
       <c r="AT31" t="n">
         <v>1.05</v>
@@ -13423,10 +13423,10 @@
         <v>13.71</v>
       </c>
       <c r="DQ31" t="n">
-        <v>11.94</v>
+        <v>11.92</v>
       </c>
       <c r="DR31" t="n">
-        <v>6.48</v>
+        <v>6.5</v>
       </c>
       <c r="DS31" t="n">
         <v>0.24</v>

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
@@ -5409,61 +5409,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="F12" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="H12" t="n">
-        <v>88.09999999999999</v>
+        <v>86.62</v>
       </c>
       <c r="I12" t="n">
         <v>-0.05</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="K12" t="n">
-        <v>4.85</v>
+        <v>4.67</v>
       </c>
       <c r="L12" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>34.8</v>
+        <v>34.1</v>
       </c>
       <c r="N12" t="n">
         <v>0.95</v>
       </c>
       <c r="O12" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="P12" t="n">
-        <v>12.4</v>
+        <v>12.86</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.3</v>
+        <v>11.86</v>
       </c>
       <c r="R12" t="n">
-        <v>5.7</v>
+        <v>5.86</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>55</v>
+        <v>54.05</v>
       </c>
       <c r="Y12" t="n">
         <v>0.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.9</v>
+        <v>14.57</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.75</v>
+        <v>8.57</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AF12" t="n">
         <v>0.16</v>
@@ -5583,67 +5583,67 @@
         <v>4.03</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.789999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI12" t="n">
         <v>4.03</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BM12" t="n">
         <v>1.08</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.08</v>
+        <v>3.98</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.74</v>
+        <v>4.68</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.87</v>
+        <v>95</v>
       </c>
       <c r="BS12" t="n">
-        <v>89.73999999999999</v>
+        <v>90</v>
       </c>
       <c r="BT12" t="n">
-        <v>82.05</v>
+        <v>82.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>61.54</v>
+        <v>62.5</v>
       </c>
       <c r="BV12" t="n">
-        <v>41.03</v>
+        <v>40</v>
       </c>
       <c r="BW12" t="n">
-        <v>23.08</v>
+        <v>22.5</v>
       </c>
       <c r="BX12" t="n">
-        <v>71.79000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CA12" t="n">
         <v>4.11</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="CC12" t="n">
         <v>2.48</v>
@@ -5655,10 +5655,10 @@
         <v>1.22</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="CH12" t="n">
         <v>1.7</v>
@@ -5718,7 +5718,7 @@
         <v>2.32</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB12" t="n">
         <v>1.15</v>
@@ -5730,46 +5730,46 @@
         <v>2.18</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.51000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="DI12" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.72</v>
+        <v>4.63</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="DM12" t="n">
-        <v>37.15</v>
+        <v>36.73</v>
       </c>
       <c r="DN12" t="n">
         <v>0.92</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.72</v>
+        <v>11.98</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.72</v>
+        <v>12</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.95</v>
+        <v>6.03</v>
       </c>
       <c r="DS12" t="n">
         <v>0.05</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>56.46</v>
+        <v>55.93</v>
       </c>
       <c r="DW12" t="n">
         <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.2</v>
+        <v>13.07</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.51</v>
+        <v>7.45</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.69</v>
+        <v>5.62</v>
       </c>
       <c r="EA12" t="n">
-        <v>8.49</v>
+        <v>8.5</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="13">
@@ -13066,13 +13066,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C31" t="n">
         <v>19</v>
       </c>
       <c r="D31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E31" t="n">
         <v>0.11</v>
@@ -13156,52 +13156,52 @@
         <v>1.79</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AI31" t="n">
-        <v>71.89</v>
+        <v>73.25</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>5.16</v>
+        <v>4.95</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="AN31" t="n">
-        <v>34.05</v>
+        <v>35.2</v>
       </c>
       <c r="AO31" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="AQ31" t="n">
-        <v>14.32</v>
+        <v>14.75</v>
       </c>
       <c r="AR31" t="n">
-        <v>11.42</v>
+        <v>11.95</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.68</v>
+        <v>6.6</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AV31" t="n">
         <v>0.05</v>
@@ -13213,82 +13213,82 @@
         <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>51.89</v>
+        <v>52.55</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA31" t="n">
-        <v>11.63</v>
+        <v>11.55</v>
       </c>
       <c r="BB31" t="n">
-        <v>7.21</v>
+        <v>7.15</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>15.53</v>
+        <v>15.65</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BF31" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="BH31" t="n">
-        <v>10.92</v>
+        <v>10.69</v>
       </c>
       <c r="BI31" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="BJ31" t="n">
         <v>0.87</v>
       </c>
       <c r="BK31" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="BL31" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="BM31" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN31" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BP31" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="BQ31" t="n">
-        <v>5.61</v>
+        <v>5.51</v>
       </c>
       <c r="BR31" t="n">
-        <v>89.47</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="BS31" t="n">
-        <v>84.20999999999999</v>
+        <v>84.62</v>
       </c>
       <c r="BT31" t="n">
-        <v>65.79000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU31" t="n">
-        <v>34.21</v>
+        <v>35.9</v>
       </c>
       <c r="BV31" t="n">
-        <v>18.42</v>
+        <v>17.95</v>
       </c>
       <c r="BW31" t="n">
-        <v>7.89</v>
+        <v>7.69</v>
       </c>
       <c r="BX31" t="n">
-        <v>57.89</v>
+        <v>58.97</v>
       </c>
       <c r="BY31" t="n">
         <v>1.81</v>
@@ -13297,31 +13297,31 @@
         <v>1.83</v>
       </c>
       <c r="CA31" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="CB31" t="n">
         <v>4.04</v>
       </c>
       <c r="CC31" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="CD31" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="CE31" t="n">
         <v>1.29</v>
       </c>
       <c r="CF31" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CG31" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="CH31" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CI31" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CJ31" t="n">
         <v>1.59</v>
@@ -13330,10 +13330,10 @@
         <v>1.42</v>
       </c>
       <c r="CL31" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM31" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CN31" t="n">
         <v>2</v>
@@ -13342,16 +13342,16 @@
         <v>1.18</v>
       </c>
       <c r="CP31" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ31" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CR31" t="n">
         <v>1.36</v>
       </c>
       <c r="CS31" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CT31" t="n">
         <v>3.26</v>
@@ -13360,22 +13360,22 @@
         <v>1.58</v>
       </c>
       <c r="CV31" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CW31" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CX31" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY31" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CZ31" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DA31" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DB31" t="n">
         <v>1.21</v>
@@ -13384,82 +13384,82 @@
         <v>1.68</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="DE31" t="n">
         <v>0.16</v>
       </c>
       <c r="DF31" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="DG31" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="DH31" t="n">
-        <v>86.34</v>
+        <v>86.67</v>
       </c>
       <c r="DI31" t="n">
         <v>0.18</v>
       </c>
       <c r="DJ31" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="DK31" t="n">
-        <v>5.95</v>
+        <v>5.82</v>
       </c>
       <c r="DL31" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM31" t="n">
-        <v>45.4</v>
+        <v>45.69</v>
       </c>
       <c r="DN31" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="DO31" t="n">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="DP31" t="n">
-        <v>13.71</v>
+        <v>13.95</v>
       </c>
       <c r="DQ31" t="n">
-        <v>11.92</v>
+        <v>12.18</v>
       </c>
       <c r="DR31" t="n">
-        <v>6.5</v>
+        <v>6.46</v>
       </c>
       <c r="DS31" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT31" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU31" t="n">
         <v>0</v>
       </c>
       <c r="DV31" t="n">
-        <v>53.6</v>
+        <v>53.9</v>
       </c>
       <c r="DW31" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX31" t="n">
-        <v>14.4</v>
+        <v>14.28</v>
       </c>
       <c r="DY31" t="n">
-        <v>9.1</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="DZ31" t="n">
-        <v>5.29</v>
+        <v>5.26</v>
       </c>
       <c r="EA31" t="n">
-        <v>14.82</v>
+        <v>14.9</v>
       </c>
       <c r="EB31" t="n">
         <v>1.58</v>
       </c>
       <c r="EC31" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
@@ -2600,7 +2600,7 @@
         <v>0.16</v>
       </c>
       <c r="F5" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="G5" t="n">
         <v>2.32</v>
@@ -2624,7 +2624,7 @@
         <v>41.63</v>
       </c>
       <c r="N5" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="O5" t="n">
         <v>2.32</v>
@@ -2912,7 +2912,7 @@
         <v>0.19</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="DG5" t="n">
         <v>2.22</v>
@@ -2936,7 +2936,7 @@
         <v>40.02</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="DO5" t="n">
         <v>2.11</v>
@@ -3496,10 +3496,10 @@
         <v>100.89</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AL7" t="n">
         <v>4.05</v>
@@ -3511,7 +3511,7 @@
         <v>40.05</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="AP7" t="n">
         <v>2</v>
@@ -3562,7 +3562,7 @@
         <v>1.27</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="BG7" t="n">
         <v>3.08</v>
@@ -3727,10 +3727,10 @@
         <v>97.45999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.03</v>
+        <v>-0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="DK7" t="n">
         <v>4.97</v>
@@ -3742,7 +3742,7 @@
         <v>46.51</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DO7" t="n">
         <v>2.49</v>
@@ -3787,7 +3787,7 @@
         <v>1.51</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="8">
@@ -4305,7 +4305,7 @@
         <v>0.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AL9" t="n">
         <v>3.83</v>
@@ -4536,7 +4536,7 @@
         <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DK9" t="n">
         <v>4.24</v>
@@ -8323,7 +8323,7 @@
         <v>0.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
         <v>2.05</v>
@@ -8335,7 +8335,7 @@
         <v>-0.05</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AL19" t="n">
         <v>3.76</v>
@@ -8398,7 +8398,7 @@
         <v>1.24</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="BG19" t="n">
         <v>2.72</v>
@@ -8554,7 +8554,7 @@
         <v>0.05</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="DG19" t="n">
         <v>2.52</v>
@@ -8566,7 +8566,7 @@
         <v>-0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="DK19" t="n">
         <v>4.92</v>
@@ -8623,7 +8623,7 @@
         <v>1.37</v>
       </c>
       <c r="EC19" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="20">

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
@@ -1875,7 +1875,7 @@
         <v>0.06</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="n">
         <v>2.17</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AL3" t="n">
         <v>3.56</v>
@@ -1950,7 +1950,7 @@
         <v>1.08</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BG3" t="n">
         <v>2.5</v>
@@ -2106,7 +2106,7 @@
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="DG3" t="n">
         <v>2.25</v>
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="DK3" t="n">
         <v>4.39</v>
@@ -2175,7 +2175,7 @@
         <v>1.23</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="4">
@@ -7114,7 +7114,7 @@
         <v>0.06</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
         <v>3.12</v>
@@ -7126,7 +7126,7 @@
         <v>0.06</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="AL16" t="n">
         <v>5.35</v>
@@ -7189,7 +7189,7 @@
         <v>1.16</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="BG16" t="n">
         <v>2.76</v>
@@ -7345,7 +7345,7 @@
         <v>0.15</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="DG16" t="n">
         <v>2.7</v>
@@ -7357,7 +7357,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DK16" t="n">
         <v>5.06</v>
@@ -7414,7 +7414,7 @@
         <v>1.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
@@ -9129,7 +9129,7 @@
         <v>0.17</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="n">
         <v>2.28</v>
@@ -9141,7 +9141,7 @@
         <v>0.06</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="AL21" t="n">
         <v>4.33</v>
@@ -9204,7 +9204,7 @@
         <v>1.58</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="BG21" t="n">
         <v>3.37</v>
@@ -9360,7 +9360,7 @@
         <v>0.2</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="DG21" t="n">
         <v>2.31</v>
@@ -9372,7 +9372,7 @@
         <v>0</v>
       </c>
       <c r="DJ21" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="DK21" t="n">
         <v>4.51</v>
@@ -9429,7 +9429,7 @@
         <v>1.63</v>
       </c>
       <c r="EC21" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="22">

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
@@ -1613,13 +1613,13 @@
         <v>3.88</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.09</v>
+        <v>4.13</v>
       </c>
       <c r="CC2" t="n">
         <v>3.95</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.22</v>
+        <v>4.32</v>
       </c>
       <c r="CE2" t="n">
         <v>1.26</v>
@@ -1664,7 +1664,7 @@
         <v>1.35</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CT2" t="n">
         <v>3.32</v>
@@ -1673,25 +1673,25 @@
         <v>1.63</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DC2" t="n">
         <v>1.57</v>
@@ -2010,13 +2010,13 @@
         <v>2.19</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CA3" t="n">
         <v>3.62</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="CC3" t="n">
         <v>3.83</v>
@@ -2067,10 +2067,10 @@
         <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CU3" t="n">
         <v>1.47</v>
@@ -2088,7 +2088,7 @@
         <v>1.81</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA3" t="n">
         <v>1.99</v>
@@ -2097,10 +2097,10 @@
         <v>1.26</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="DE3" t="n">
         <v>0.08</v>
@@ -2816,13 +2816,13 @@
         <v>2.13</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CA5" t="n">
         <v>3.8</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="CC5" t="n">
         <v>3.43</v>
@@ -2873,7 +2873,7 @@
         <v>1.35</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CT5" t="n">
         <v>3.28</v>
@@ -2897,7 +2897,7 @@
         <v>2.4</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DB5" t="n">
         <v>1.18</v>
@@ -2906,7 +2906,7 @@
         <v>1.58</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DE5" t="n">
         <v>0.19</v>
@@ -4037,7 +4037,7 @@
         <v>4.66</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.07</v>
+        <v>5.2</v>
       </c>
       <c r="CE8" t="n">
         <v>1.3</v>
@@ -4082,40 +4082,40 @@
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CT8" t="n">
         <v>3.21</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX8" t="n">
         <v>1.6</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.28</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="DB8" t="n">
         <v>1.22</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="DE8" t="n">
         <v>0.09</v>
@@ -4831,13 +4831,13 @@
         <v>2.46</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CA10" t="n">
         <v>3.85</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="CC10" t="n">
         <v>4.53</v>
@@ -4888,16 +4888,16 @@
         <v>1.37</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CU10" t="n">
         <v>1.6</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CW10" t="n">
         <v>1.62</v>
@@ -4921,7 +4921,7 @@
         <v>1.66</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
@@ -5240,13 +5240,13 @@
         <v>3.61</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CC11" t="n">
         <v>3.9</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.04</v>
+        <v>3.97</v>
       </c>
       <c r="CE11" t="n">
         <v>1.33</v>
@@ -5291,7 +5291,7 @@
         <v>1.38</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CT11" t="n">
         <v>3.18</v>
@@ -5300,22 +5300,22 @@
         <v>1.5</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CW11" t="n">
         <v>1.68</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY11" t="n">
         <v>1.84</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB11" t="n">
         <v>1.25</v>
@@ -5324,7 +5324,7 @@
         <v>1.8</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>2.09</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CA13" t="n">
         <v>3.77</v>
       </c>
       <c r="CB13" t="n">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="CC13" t="n">
         <v>4.13</v>
@@ -6121,7 +6121,7 @@
         <v>2.44</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DB13" t="n">
         <v>1.18</v>
@@ -6443,7 +6443,7 @@
         <v>1.59</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CA14" t="n">
         <v>3.86</v>
@@ -6455,7 +6455,7 @@
         <v>2.48</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CE14" t="n">
         <v>1.31</v>
@@ -6500,7 +6500,7 @@
         <v>1.37</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CT14" t="n">
         <v>3.21</v>
@@ -6509,7 +6509,7 @@
         <v>1.57</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CW14" t="n">
         <v>1.68</v>
@@ -6521,10 +6521,10 @@
         <v>1.85</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB14" t="n">
         <v>1.22</v>
@@ -6852,13 +6852,13 @@
         <v>3.59</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="CC15" t="n">
         <v>3.25</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="CE15" t="n">
         <v>1.28</v>
@@ -6903,19 +6903,19 @@
         <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX15" t="n">
         <v>1.55</v>
@@ -6927,16 +6927,16 @@
         <v>2.41</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB15" t="n">
         <v>1.23</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="DE15" t="n">
         <v>0.11</v>
@@ -7255,13 +7255,13 @@
         <v>3.91</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.09</v>
+        <v>4.12</v>
       </c>
       <c r="CC16" t="n">
         <v>5.45</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.98</v>
+        <v>6.1</v>
       </c>
       <c r="CE16" t="n">
         <v>1.26</v>
@@ -7303,19 +7303,19 @@
         <v>2.55</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CW16" t="n">
         <v>1.67</v>
@@ -7324,22 +7324,22 @@
         <v>1.59</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.3</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DB16" t="n">
         <v>1.21</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="DE16" t="n">
         <v>0.15</v>
@@ -7658,7 +7658,7 @@
         <v>3.77</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="CC17" t="n">
         <v>3.17</v>
@@ -7718,10 +7718,10 @@
         <v>1.56</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX17" t="n">
         <v>1.6</v>
@@ -7730,10 +7730,10 @@
         <v>2</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB17" t="n">
         <v>1.22</v>
@@ -8458,7 +8458,7 @@
         <v>1.96</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CA19" t="n">
         <v>3.68</v>
@@ -8867,13 +8867,13 @@
         <v>3.61</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC20" t="n">
         <v>3.54</v>
       </c>
       <c r="CD20" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CE20" t="n">
         <v>1.34</v>
@@ -8918,13 +8918,13 @@
         <v>1.39</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CT20" t="n">
         <v>3.11</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV20" t="n">
         <v>2.28</v>
@@ -8948,10 +8948,10 @@
         <v>1.26</v>
       </c>
       <c r="DC20" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="DE20" t="n">
         <v>0.09</v>
@@ -9673,13 +9673,13 @@
         <v>3.74</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="CC22" t="n">
         <v>3.15</v>
       </c>
       <c r="CD22" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="CE22" t="n">
         <v>1.29</v>
@@ -9724,16 +9724,16 @@
         <v>1.36</v>
       </c>
       <c r="CS22" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CT22" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="CU22" t="n">
         <v>1.56</v>
       </c>
       <c r="CV22" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CW22" t="n">
         <v>1.61</v>
@@ -9754,10 +9754,10 @@
         <v>1.21</v>
       </c>
       <c r="DC22" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DD22" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="DE22" t="n">
         <v>0.22</v>
@@ -10082,7 +10082,7 @@
         <v>4.1</v>
       </c>
       <c r="CD23" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="CE23" t="n">
         <v>1.27</v>
@@ -10127,7 +10127,7 @@
         <v>1.35</v>
       </c>
       <c r="CS23" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CT23" t="n">
         <v>3.31</v>
@@ -10154,7 +10154,7 @@
         <v>2.01</v>
       </c>
       <c r="DB23" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="DC23" t="n">
         <v>1.62</v>
@@ -10876,13 +10876,13 @@
         <v>2.18</v>
       </c>
       <c r="BZ25" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CA25" t="n">
         <v>3.8</v>
       </c>
       <c r="CB25" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="CC25" t="n">
         <v>3.61</v>
@@ -10951,13 +10951,13 @@
         <v>1.46</v>
       </c>
       <c r="CY25" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CZ25" t="n">
         <v>2.56</v>
       </c>
       <c r="DA25" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DB25" t="n">
         <v>1.16</v>
@@ -10966,7 +10966,7 @@
         <v>1.53</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DE25" t="n">
         <v>0.09</v>
@@ -11279,13 +11279,13 @@
         <v>1.8</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CA26" t="n">
         <v>3.74</v>
       </c>
       <c r="CB26" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CC26" t="n">
         <v>2.73</v>
@@ -11339,7 +11339,7 @@
         <v>2.48</v>
       </c>
       <c r="CT26" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CU26" t="n">
         <v>1.59</v>
@@ -11351,16 +11351,16 @@
         <v>1.6</v>
       </c>
       <c r="CX26" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY26" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ26" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DA26" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DB26" t="n">
         <v>1.2</v>
@@ -11682,7 +11682,7 @@
         <v>1.68</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CA27" t="n">
         <v>3.75</v>
@@ -11739,7 +11739,7 @@
         <v>1.4</v>
       </c>
       <c r="CS27" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CT27" t="n">
         <v>3.06</v>
@@ -11748,10 +11748,10 @@
         <v>1.5</v>
       </c>
       <c r="CV27" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CW27" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX27" t="n">
         <v>1.5</v>
@@ -11769,10 +11769,10 @@
         <v>1.26</v>
       </c>
       <c r="DC27" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DD27" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="DE27" t="n">
         <v>0.14</v>
@@ -12897,13 +12897,13 @@
         <v>3.77</v>
       </c>
       <c r="CB30" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="CC30" t="n">
         <v>5.29</v>
       </c>
       <c r="CD30" t="n">
-        <v>6</v>
+        <v>5.97</v>
       </c>
       <c r="CE30" t="n">
         <v>1.32</v>
@@ -12948,7 +12948,7 @@
         <v>1.38</v>
       </c>
       <c r="CS30" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CT30" t="n">
         <v>3.18</v>
@@ -12957,7 +12957,7 @@
         <v>1.5</v>
       </c>
       <c r="CV30" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CW30" t="n">
         <v>1.75</v>
@@ -12969,13 +12969,13 @@
         <v>1.99</v>
       </c>
       <c r="CZ30" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DA30" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB30" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC30" t="n">
         <v>1.79</v>
@@ -13300,13 +13300,13 @@
         <v>3.86</v>
       </c>
       <c r="CB31" t="n">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="CC31" t="n">
         <v>3.07</v>
       </c>
       <c r="CD31" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CE31" t="n">
         <v>1.29</v>
@@ -13351,13 +13351,13 @@
         <v>1.36</v>
       </c>
       <c r="CS31" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CT31" t="n">
         <v>3.26</v>
       </c>
       <c r="CU31" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CV31" t="n">
         <v>2.4</v>
@@ -13381,10 +13381,10 @@
         <v>1.21</v>
       </c>
       <c r="DC31" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="DE31" t="n">
         <v>0.16</v>

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
@@ -1613,13 +1613,13 @@
         <v>3.88</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.13</v>
+        <v>4.09</v>
       </c>
       <c r="CC2" t="n">
         <v>3.95</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.32</v>
+        <v>4.22</v>
       </c>
       <c r="CE2" t="n">
         <v>1.26</v>
@@ -1664,7 +1664,7 @@
         <v>1.35</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CT2" t="n">
         <v>3.32</v>
@@ -1673,25 +1673,25 @@
         <v>1.63</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="DC2" t="n">
         <v>1.57</v>
@@ -2010,13 +2010,13 @@
         <v>2.19</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CA3" t="n">
         <v>3.62</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CC3" t="n">
         <v>3.83</v>
@@ -2067,10 +2067,10 @@
         <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CU3" t="n">
         <v>1.47</v>
@@ -2088,7 +2088,7 @@
         <v>1.81</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="DA3" t="n">
         <v>1.99</v>
@@ -2097,10 +2097,10 @@
         <v>1.26</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="DE3" t="n">
         <v>0.08</v>
@@ -2816,13 +2816,13 @@
         <v>2.13</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CA5" t="n">
         <v>3.8</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CC5" t="n">
         <v>3.43</v>
@@ -2873,7 +2873,7 @@
         <v>1.35</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CT5" t="n">
         <v>3.28</v>
@@ -2897,7 +2897,7 @@
         <v>2.4</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB5" t="n">
         <v>1.18</v>
@@ -2906,7 +2906,7 @@
         <v>1.58</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DE5" t="n">
         <v>0.19</v>
@@ -4037,7 +4037,7 @@
         <v>4.66</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.2</v>
+        <v>5.07</v>
       </c>
       <c r="CE8" t="n">
         <v>1.3</v>
@@ -4082,40 +4082,40 @@
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CT8" t="n">
         <v>3.21</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX8" t="n">
         <v>1.6</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.28</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DB8" t="n">
         <v>1.22</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="DE8" t="n">
         <v>0.09</v>
@@ -4831,13 +4831,13 @@
         <v>2.46</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CA10" t="n">
         <v>3.85</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="CC10" t="n">
         <v>4.53</v>
@@ -4888,16 +4888,16 @@
         <v>1.37</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CU10" t="n">
         <v>1.6</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CW10" t="n">
         <v>1.62</v>
@@ -4921,7 +4921,7 @@
         <v>1.66</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
@@ -5240,13 +5240,13 @@
         <v>3.61</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="CC11" t="n">
         <v>3.9</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="CE11" t="n">
         <v>1.33</v>
@@ -5291,7 +5291,7 @@
         <v>1.38</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CT11" t="n">
         <v>3.18</v>
@@ -5300,22 +5300,22 @@
         <v>1.5</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW11" t="n">
         <v>1.68</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY11" t="n">
         <v>1.84</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB11" t="n">
         <v>1.25</v>
@@ -5324,7 +5324,7 @@
         <v>1.8</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>2.09</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CA13" t="n">
         <v>3.77</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="CC13" t="n">
         <v>4.13</v>
@@ -6121,7 +6121,7 @@
         <v>2.44</v>
       </c>
       <c r="DA13" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DB13" t="n">
         <v>1.18</v>
@@ -6443,7 +6443,7 @@
         <v>1.59</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CA14" t="n">
         <v>3.86</v>
@@ -6455,7 +6455,7 @@
         <v>2.48</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CE14" t="n">
         <v>1.31</v>
@@ -6500,7 +6500,7 @@
         <v>1.37</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CT14" t="n">
         <v>3.21</v>
@@ -6509,7 +6509,7 @@
         <v>1.57</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW14" t="n">
         <v>1.68</v>
@@ -6521,10 +6521,10 @@
         <v>1.85</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB14" t="n">
         <v>1.22</v>
@@ -6852,13 +6852,13 @@
         <v>3.59</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CC15" t="n">
         <v>3.25</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
       <c r="CE15" t="n">
         <v>1.28</v>
@@ -6903,19 +6903,19 @@
         <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX15" t="n">
         <v>1.55</v>
@@ -6927,16 +6927,16 @@
         <v>2.41</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB15" t="n">
         <v>1.23</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="DE15" t="n">
         <v>0.11</v>
@@ -7255,13 +7255,13 @@
         <v>3.91</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.12</v>
+        <v>4.09</v>
       </c>
       <c r="CC16" t="n">
         <v>5.45</v>
       </c>
       <c r="CD16" t="n">
-        <v>6.1</v>
+        <v>5.98</v>
       </c>
       <c r="CE16" t="n">
         <v>1.26</v>
@@ -7303,19 +7303,19 @@
         <v>2.55</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW16" t="n">
         <v>1.67</v>
@@ -7324,22 +7324,22 @@
         <v>1.59</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.3</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB16" t="n">
         <v>1.21</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="DE16" t="n">
         <v>0.15</v>
@@ -7658,7 +7658,7 @@
         <v>3.77</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CC17" t="n">
         <v>3.17</v>
@@ -7718,10 +7718,10 @@
         <v>1.56</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX17" t="n">
         <v>1.6</v>
@@ -7730,10 +7730,10 @@
         <v>2</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DB17" t="n">
         <v>1.22</v>
@@ -8458,7 +8458,7 @@
         <v>1.96</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CA19" t="n">
         <v>3.68</v>
@@ -8867,13 +8867,13 @@
         <v>3.61</v>
       </c>
       <c r="CB20" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CC20" t="n">
         <v>3.54</v>
       </c>
       <c r="CD20" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="CE20" t="n">
         <v>1.34</v>
@@ -8918,13 +8918,13 @@
         <v>1.39</v>
       </c>
       <c r="CS20" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CT20" t="n">
         <v>3.11</v>
       </c>
       <c r="CU20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV20" t="n">
         <v>2.28</v>
@@ -8948,10 +8948,10 @@
         <v>1.26</v>
       </c>
       <c r="DC20" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DD20" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="DE20" t="n">
         <v>0.09</v>
@@ -9673,13 +9673,13 @@
         <v>3.74</v>
       </c>
       <c r="CB22" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CC22" t="n">
         <v>3.15</v>
       </c>
       <c r="CD22" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="CE22" t="n">
         <v>1.29</v>
@@ -9724,16 +9724,16 @@
         <v>1.36</v>
       </c>
       <c r="CS22" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CT22" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CU22" t="n">
         <v>1.56</v>
       </c>
       <c r="CV22" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW22" t="n">
         <v>1.61</v>
@@ -9754,10 +9754,10 @@
         <v>1.21</v>
       </c>
       <c r="DC22" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DD22" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="DE22" t="n">
         <v>0.22</v>
@@ -10082,7 +10082,7 @@
         <v>4.1</v>
       </c>
       <c r="CD23" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="CE23" t="n">
         <v>1.27</v>
@@ -10127,7 +10127,7 @@
         <v>1.35</v>
       </c>
       <c r="CS23" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CT23" t="n">
         <v>3.31</v>
@@ -10154,7 +10154,7 @@
         <v>2.01</v>
       </c>
       <c r="DB23" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DC23" t="n">
         <v>1.62</v>
@@ -10876,13 +10876,13 @@
         <v>2.18</v>
       </c>
       <c r="BZ25" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CA25" t="n">
         <v>3.8</v>
       </c>
       <c r="CB25" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="CC25" t="n">
         <v>3.61</v>
@@ -10951,13 +10951,13 @@
         <v>1.46</v>
       </c>
       <c r="CY25" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CZ25" t="n">
         <v>2.56</v>
       </c>
       <c r="DA25" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DB25" t="n">
         <v>1.16</v>
@@ -10966,7 +10966,7 @@
         <v>1.53</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DE25" t="n">
         <v>0.09</v>
@@ -11279,13 +11279,13 @@
         <v>1.8</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CA26" t="n">
         <v>3.74</v>
       </c>
       <c r="CB26" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="CC26" t="n">
         <v>2.73</v>
@@ -11339,7 +11339,7 @@
         <v>2.48</v>
       </c>
       <c r="CT26" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CU26" t="n">
         <v>1.59</v>
@@ -11351,16 +11351,16 @@
         <v>1.6</v>
       </c>
       <c r="CX26" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY26" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ26" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DA26" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB26" t="n">
         <v>1.2</v>
@@ -11682,7 +11682,7 @@
         <v>1.68</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CA27" t="n">
         <v>3.75</v>
@@ -11739,7 +11739,7 @@
         <v>1.4</v>
       </c>
       <c r="CS27" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CT27" t="n">
         <v>3.06</v>
@@ -11748,10 +11748,10 @@
         <v>1.5</v>
       </c>
       <c r="CV27" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CW27" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX27" t="n">
         <v>1.5</v>
@@ -11769,10 +11769,10 @@
         <v>1.26</v>
       </c>
       <c r="DC27" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD27" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="DE27" t="n">
         <v>0.14</v>
@@ -12897,13 +12897,13 @@
         <v>3.77</v>
       </c>
       <c r="CB30" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="CC30" t="n">
         <v>5.29</v>
       </c>
       <c r="CD30" t="n">
-        <v>5.97</v>
+        <v>6</v>
       </c>
       <c r="CE30" t="n">
         <v>1.32</v>
@@ -12948,7 +12948,7 @@
         <v>1.38</v>
       </c>
       <c r="CS30" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CT30" t="n">
         <v>3.18</v>
@@ -12957,7 +12957,7 @@
         <v>1.5</v>
       </c>
       <c r="CV30" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CW30" t="n">
         <v>1.75</v>
@@ -12969,13 +12969,13 @@
         <v>1.99</v>
       </c>
       <c r="CZ30" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DA30" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DB30" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DC30" t="n">
         <v>1.79</v>
@@ -13300,13 +13300,13 @@
         <v>3.86</v>
       </c>
       <c r="CB31" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="CC31" t="n">
         <v>3.07</v>
       </c>
       <c r="CD31" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CE31" t="n">
         <v>1.29</v>
@@ -13351,13 +13351,13 @@
         <v>1.36</v>
       </c>
       <c r="CS31" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CT31" t="n">
         <v>3.26</v>
       </c>
       <c r="CU31" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV31" t="n">
         <v>2.4</v>
@@ -13381,10 +13381,10 @@
         <v>1.21</v>
       </c>
       <c r="DC31" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="DE31" t="n">
         <v>0.16</v>

--- a/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
+++ b/data/teams/leagues/Averages_USA_Major_League_Soccer_2025.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,667 +694,667 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
